--- a/astro-site/public/dl/ghost-kitchen-checklist-templates/02-cloud-kitchen-station-checklists.xlsx
+++ b/astro-site/public/dl/ghost-kitchen-checklist-templates/02-cloud-kitchen-station-checklists.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>Preheat griddle, oven and burners for today's menus</t>
+          <t>Preheat griddle, oven and burners for today's menus; ice-point check the probe thermometer (32 °F) and recalibrate it if it's off</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>Prep proteins by brand: chicken, beef, fish — cook each to temp, probe in the center: chicken 165 °F, ground beef 155 °F for 17 s, fish 145 °F for 15 s (FDA 3-401.11); keep raw on the bottom shelf, away from ready-to-eat (FDA 3-302.11)</t>
+          <t>Prep proteins by brand: chicken, beef, fish — cook each to temp, probe in the center: chicken 165 °F, ground beef 155 °F for 17 s, fish 145 °F for 15 s (FDA 3-401.11); store raw below ready-to-eat, with raw chicken on the very bottom, under beef and fish (FDA 3-302.11)</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -1014,9 +1014,9 @@
       <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>Cook to each brand's tickets</t>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Cook to each brand's tickets; wash, rinse and sanitize tongs, spatulas and cutting boards at least every 4 h during service, or swap in clean ones (FDA 4-602.11)</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>Store prepped items labeled — date marking: ready-to-eat food keeps 7 days at 41 °F, prep day = day 1 (FDA 3-501.17)</t>
+          <t>Store prepped items labeled — date marking: 7 days max at 41 °F, prep day = day 1 (FDA 3-501.17), or the kit's shorter limit (05 "Weekly FIFO Check")</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>Prep bases: sushi rice, quinoa, lettuce — sushi rice acidified to hold out of the cooler needs a variance and a HACCP plan from the health department (FDA 3-502.11(D)); otherwise keep it at 41 °F or below, or use time as a public health control: written procedure, time marked, discard at 4 h (FDA 3-501.19)</t>
+          <t>Prep bases: sushi rice, quinoa, lettuce — sushi rice acidified to hold out of the cooler needs a variance from the health department and a HACCP plan it approves (FDA 3-502.11(D)); otherwise keep it at 41 °F or below, or use time as a public health control: written procedure, time marked, discard at 4 h (FDA 3-501.19)</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>Fish served RAW, marinated or partly raw (poke, sushi, tartare, ceviche) — parasite destruction: use only fish frozen at −4 °F or below for 7 days, or at −31 °F or below until solid plus 15 h (FDA 3-402.11); keep the freezing record, or the supplier's written statement, for 90 days (FDA 3-402.12); consumer advisory on each app listing (FDA 3-603.11). A regular 0 °F freezer does not count</t>
+          <t>Fish served RAW, marinated or partly raw (poke, sushi, tartare, ceviche) — parasite destruction (FDA 3-402.11): frozen and stored at −4 °F or below for 7 days; or frozen at −31 °F or below until solid and stored at −31 °F or below for 15 h; or frozen at −31 °F or below until solid and stored at −4 °F or below for 24 h. Keep the freezing record, or the supplier's written statement, for 90 days (FDA 3-402.12); consumer advisory on each app listing (FDA 3-603.11). A regular 0 °F freezer does not count</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -1669,9 +1669,9 @@
       <c r="A15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Keep inserts restocked</t>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Keep inserts restocked; swap serving spoons, tongs and cutting boards for clean, sanitized ones at least every 4 h (FDA 4-602.11)</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>Cover and refrigerate all inserts — date marking: ready-to-eat food keeps 7 days at 41 °F, prep day = day 1 (FDA 3-501.17)</t>
+          <t>Cover and refrigerate all inserts — date marking: 7 days max at 41 °F, prep day = day 1 (FDA 3-501.17), or the kit's shorter limit (05 "Weekly FIFO Check")</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>Discard cut fruit/vegetables older than 24 h (kit standard); cut leafy greens, tomatoes and melon are TCS: 41 °F or below and date marked (FDA 3-501.16, 3-501.17)</t>
+          <t>Discard cut fruit older than 24 h and cut vegetables older than 2 days (kit standard, same as the "Weekly FIFO Check" tab in 05); cut leafy greens, tomatoes and melon are TCS: 41 °F or below and date marked (FDA 3-501.16, 3-501.17)</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
